--- a/studio-di-fattibilita/allegati/A7-Link-Budget/LINK-BUDGET-v1.0.xlsx
+++ b/studio-di-fattibilita/allegati/A7-Link-Budget/LINK-BUDGET-v1.0.xlsx
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>127.86</t>
+          <t>127.88</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>79.61</t>
+          <t>79.60</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>136.44</t>
+          <t>136.46</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>80.03</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>135.64</t>
+          <t>136.07</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>76.34</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="C125" s="15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>134.38</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>94.22</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>134.38</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>97.08</t>
+          <t>97.00</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>160.06</t>
+          <t>159.52</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>142.96</t>
+          <t>143.06</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>94.50</t>
+          <t>94.40</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="C125" s="15" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>81.44</t>
+          <t>81.12</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>191.27</t>
+          <t>191.26</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>154.83</t>
+          <t>157.17</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>143.50</t>
+          <t>141.15</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>59.52</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>4942.74</t>
+          <t>4748.30</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>11.48</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>158.39</t>
+          <t>165.51</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>131.57</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>46.59</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>4543.52</t>
+          <t>3951.92</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>153.35</t>
+          <t>155.30</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>144.98</t>
+          <t>143.03</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>51.47</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="C129" s="15" t="inlineStr">
         <is>
-          <t>4117.19</t>
+          <t>3987.32</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="I2" s="15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J2" s="15" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="K2" s="15" t="inlineStr">
         <is>
-          <t>127.86</t>
+          <t>127.88</t>
         </is>
       </c>
       <c r="L2" s="15" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>79.61</t>
+          <t>79.60</t>
         </is>
       </c>
       <c r="N2" s="15" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="O2" s="15" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="P2" s="15" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="Q2" s="15" t="inlineStr">
         <is>
-          <t>18.61</t>
+          <t>18.60</t>
         </is>
       </c>
       <c r="R2" s="15" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="I3" s="15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" s="15" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="K3" s="15" t="inlineStr">
         <is>
-          <t>136.44</t>
+          <t>136.46</t>
         </is>
       </c>
       <c r="L3" s="15" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>80.03</t>
         </is>
       </c>
       <c r="N3" s="15" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="O3" s="15" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="P3" s="15" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="Q3" s="15" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="R3" s="15" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="J4" s="15" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
-          <t>135.64</t>
+          <t>136.07</t>
         </is>
       </c>
       <c r="L4" s="15" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="M4" s="15" t="inlineStr">
         <is>
-          <t>76.34</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="N4" s="15" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="O4" s="15" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>8.91</t>
         </is>
       </c>
       <c r="P4" s="15" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="Q4" s="15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="R4" s="15" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="T4" s="15" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="U4" s="15" t="inlineStr">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>134.38</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="L6" s="15" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="N6" s="15" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="O6" s="15" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="P6" s="15" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="Q6" s="15" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="R6" s="15" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="T6" s="15" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>94.22</t>
         </is>
       </c>
       <c r="U6" s="15" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>134.38</t>
+          <t>134.46</t>
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>97.08</t>
+          <t>97.00</t>
         </is>
       </c>
       <c r="N7" s="15" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="O7" s="15" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="P7" s="15" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="Q7" s="15" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="R7" s="15" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="T7" s="15" t="inlineStr">
         <is>
-          <t>160.06</t>
+          <t>159.52</t>
         </is>
       </c>
       <c r="U7" s="15" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>142.96</t>
+          <t>143.06</t>
         </is>
       </c>
       <c r="L8" s="15" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="M8" s="15" t="inlineStr">
         <is>
-          <t>94.50</t>
+          <t>94.40</t>
         </is>
       </c>
       <c r="N8" s="15" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="O8" s="15" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="P8" s="15" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="Q8" s="15" t="inlineStr">
         <is>
-          <t>16.50</t>
+          <t>16.40</t>
         </is>
       </c>
       <c r="R8" s="15" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="T8" s="15" t="inlineStr">
         <is>
-          <t>81.44</t>
+          <t>81.12</t>
         </is>
       </c>
       <c r="U8" s="15" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="T9" s="15" t="inlineStr">
         <is>
-          <t>191.27</t>
+          <t>191.26</t>
         </is>
       </c>
       <c r="U9" s="15" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="T10" s="15" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="U10" s="15" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
-          <t>154.83</t>
+          <t>157.17</t>
         </is>
       </c>
       <c r="L13" s="15" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>143.50</t>
+          <t>141.15</t>
         </is>
       </c>
       <c r="N13" s="15" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
-          <t>59.52</t>
+          <t>57.18</t>
         </is>
       </c>
       <c r="P13" s="15" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="R13" s="15" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="T13" s="15" t="inlineStr">
         <is>
-          <t>4942.74</t>
+          <t>4748.30</t>
         </is>
       </c>
       <c r="U13" s="15" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>11.48</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>158.39</t>
+          <t>165.51</t>
         </is>
       </c>
       <c r="L14" s="15" t="inlineStr">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>131.57</t>
         </is>
       </c>
       <c r="N14" s="15" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="O14" s="15" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="P14" s="15" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="Q14" s="15" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>46.59</t>
         </is>
       </c>
       <c r="R14" s="15" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="T14" s="15" t="inlineStr">
         <is>
-          <t>4543.52</t>
+          <t>3951.92</t>
         </is>
       </c>
       <c r="U14" s="15" t="inlineStr">
@@ -14943,7 +14943,7 @@
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>153.35</t>
+          <t>155.30</t>
         </is>
       </c>
       <c r="L15" s="15" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>144.98</t>
+          <t>143.03</t>
         </is>
       </c>
       <c r="N15" s="15" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="O15" s="15" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="P15" s="15" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="Q15" s="15" t="inlineStr">
         <is>
-          <t>51.47</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="R15" s="15" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="T15" s="15" t="inlineStr">
         <is>
-          <t>4117.19</t>
+          <t>3987.32</t>
         </is>
       </c>
       <c r="U15" s="15" t="inlineStr">
@@ -15144,22 +15144,22 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>102.21</v>
+        <v>102.2</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>94.25</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>88.23</v>
+        <v>88.22</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>84.70999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>82.20999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>78.69</v>
+        <v>78.68000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -15169,22 +15169,22 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>92.93000000000001</v>
+        <v>92.38</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>84.97</v>
+        <v>84.42</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>78.95</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>75.43000000000001</v>
+        <v>74.87</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>72.93000000000001</v>
+        <v>72.38</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>69.40000000000001</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -15194,22 +15194,22 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>85.56</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>77.59999999999999</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>71.58</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>68.06</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>65.56</v>
+        <v>63.24</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>62.04</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="10">
@@ -15219,22 +15219,22 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>84.23999999999999</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>76.29000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>70.26000000000001</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>66.73999999999999</v>
+        <v>63.99</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>64.23999999999999</v>
+        <v>61.49</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>60.72</v>
+        <v>57.97</v>
       </c>
     </row>
     <row r="11">
@@ -15244,22 +15244,22 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>78.2</v>
+        <v>73.23</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>70.23999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>64.22</v>
+        <v>59.25</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>60.7</v>
+        <v>55.73</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>58.2</v>
+        <v>53.23</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>54.68</v>
+        <v>49.71</v>
       </c>
     </row>
   </sheetData>
@@ -15368,7 +15368,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
@@ -15378,25 +15378,25 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="7">
@@ -15406,25 +15406,25 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.36</v>
+        <v>1.02</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.68</v>
+        <v>1.98</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>2.51</v>
+        <v>2.9</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>6.22</v>
       </c>
     </row>
     <row r="8">
@@ -15434,25 +15434,25 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>0.75</v>
+        <v>2.03</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.96</v>
+        <v>2.56</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1.21</v>
+        <v>3.17</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>9.609999999999999</v>
+        <v>4.32</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>21.83</v>
       </c>
     </row>
     <row r="9">
@@ -15462,25 +15462,25 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.47</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>1.2</v>
+        <v>3.11</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>3.67</v>
+        <v>3.84</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>9.48</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>11.54</v>
+        <v>13.28</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>25.7</v>
       </c>
     </row>
     <row r="10">
@@ -15490,25 +15490,25 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>10.58</v>
+        <v>4.87</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>24.3</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>21.75</v>
+        <v>45.14</v>
       </c>
     </row>
   </sheetData>

--- a/studio-di-fattibilita/allegati/A7-Link-Budget/LINK-BUDGET-v1.0.xlsx
+++ b/studio-di-fattibilita/allegati/A7-Link-Budget/LINK-BUDGET-v1.0.xlsx
@@ -15522,13 +15522,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15541,283 +15541,360 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Formula: closed-form solve da L_fs(d) tale che SNR_required = 11 dB. HAPS alt 20 km, P_tx 25 W, BW 20 MHz / 250 MHz, UE G/T -25.6 dB/K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+          <t>Formula: closed-form solve da L_fs(d) tale che SNR_required = 11 dB. HAPS alt 20 km, P_tx 25 W. S-band BW 20 MHz, 700 MHz BW 10 MHz, Ka BW 250 MHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>S-band e 700 MHz: receiver = UE handheld (G/T=-25.6 dB/K). Ka 31 GHz: receiver = Gateway (G/T=+24 dB/K, rain fade 4 dB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Antenna gain [dBi]</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Cell radius S-band 2.1 GHz [km]</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Cell radius 700 MHz [km]</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>Cell radius Ka 31 GHz [km]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>118.2</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0</v>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Cell radius Ka 31 GHz (Gateway) [km]</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="15" t="n">
-        <v>29.8</v>
+        <v>20.3</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>149.6</v>
+        <v>118.2</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>0</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>40.5</v>
+        <v>29.8</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>189</v>
+        <v>149.6</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="15" t="n">
-        <v>53.2</v>
+        <v>40.5</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>238.4</v>
+        <v>189</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0</v>
+        <v>163.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="15" t="n">
-        <v>68.7</v>
+        <v>53.2</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>300.5</v>
+        <v>238.4</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0</v>
+        <v>206.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>87.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>378.6</v>
+        <v>300.5</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0</v>
+        <v>260.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>111.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>476.9</v>
+        <v>378.6</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>0</v>
+        <v>328.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="15" t="n">
-        <v>141.4</v>
+        <v>111.7</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>600.6</v>
+        <v>476.9</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0</v>
+        <v>413.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="15" t="n">
-        <v>178.7</v>
+        <v>141.4</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>756.2</v>
+        <v>600.6</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0</v>
+        <v>521.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="15" t="n">
-        <v>225.5</v>
+        <v>178.7</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>952.2</v>
+        <v>756.2</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0</v>
+        <v>656.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="15" t="n">
-        <v>284.3</v>
+        <v>225.5</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>1198.8</v>
+        <v>952.2</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>0</v>
+        <v>826.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="15" t="n">
-        <v>358.3</v>
+        <v>284.3</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>1509.3</v>
+        <v>1198.8</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0</v>
+        <v>1040.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" s="15" t="n">
-        <v>451.3</v>
+        <v>358.3</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>1900.2</v>
+        <v>1509.3</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0</v>
+        <v>1309.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" s="15" t="n">
-        <v>568.4</v>
+        <v>451.3</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>2392.2</v>
+        <v>1900.2</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0</v>
+        <v>1649.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" s="15" t="n">
-        <v>715.7</v>
+        <v>568.4</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>3011.7</v>
+        <v>2392.2</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>0</v>
+        <v>2076.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="15" t="n">
-        <v>901.1</v>
+        <v>715.7</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>3791.5</v>
+        <v>3011.7</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0</v>
+        <v>2613.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B21" s="15" t="n">
-        <v>1134.5</v>
+        <v>901.1</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>4773.2</v>
+        <v>3791.5</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>8.5</v>
+        <v>3290.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>1134.5</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>4773.2</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>4142.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B23" s="15" t="n">
         <v>1428.4</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C23" s="15" t="n">
         <v>6009.2</v>
       </c>
-      <c r="D22" s="15" t="n">
-        <v>18.7</v>
+      <c r="D23" s="15" t="n">
+        <v>5215.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>1798.3</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>7565.1</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>6565.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>2264</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>9523.9</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>8265.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>2850.2</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>11989.9</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>10406.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>3588.2</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>15094.4</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>13100.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>4517.3</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>19002.8</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>16492.6</v>
       </c>
     </row>
   </sheetData>
